--- a/Modules/VU/VU_BOM.xlsx
+++ b/Modules/VU/VU_BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\My-Dev\Modular Synth\Avalon Harmonics\VU\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F797931-A791-4890-922F-E1C5EAAC6FE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BAA3DFF-DDB8-4411-A246-89D5A7035272}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BOM" sheetId="1" r:id="rId1"/>
@@ -107,15 +107,9 @@
     <t>Pushernut</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/black-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Gold</t>
   </si>
   <si>
-    <t>https://pushermanproductions.com/product/pushernuts-gold-smooth-edge-jack-nuts-pack-of-25/</t>
-  </si>
-  <si>
     <t>Jack Nut</t>
   </si>
   <si>
@@ -747,6 +741,12 @@
       </rPr>
       <t>J_OUT</t>
     </r>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57164621578504</t>
+  </si>
+  <si>
+    <t>https://pushermanproductions.com/products/pushernuts-round-mini-jack-nuts-pack-of-25?variant=57166910816520</t>
   </si>
 </sst>
 </file>
@@ -1709,7 +1709,7 @@
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="J2" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -1744,19 +1744,19 @@
         <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -1767,19 +1767,19 @@
         <v>9</v>
       </c>
       <c r="C4" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -1790,19 +1790,19 @@
         <v>8</v>
       </c>
       <c r="C5" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E5" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -1810,22 +1810,22 @@
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
@@ -1836,19 +1836,19 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" t="s">
+        <v>103</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="D7" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" t="s">
-        <v>105</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="J7" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
@@ -1856,22 +1856,22 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -1879,22 +1879,22 @@
         <v>1</v>
       </c>
       <c r="B9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C9" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D9" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E9" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1902,22 +1902,22 @@
         <v>1</v>
       </c>
       <c r="B10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C10" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="D10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
@@ -1925,22 +1925,22 @@
         <v>1</v>
       </c>
       <c r="B11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
+        <v>106</v>
+      </c>
+      <c r="D11" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D11" t="s">
-        <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>107</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
@@ -1951,19 +1951,19 @@
         <v>6</v>
       </c>
       <c r="C12" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D12" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
+        <v>105</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="J12" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
@@ -1971,22 +1971,22 @@
         <v>1</v>
       </c>
       <c r="B13" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C13" t="s">
+        <v>111</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
+        <v>109</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D13" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" t="s">
-        <v>111</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
@@ -1997,19 +1997,19 @@
         <v>5</v>
       </c>
       <c r="C14" t="s">
+        <v>110</v>
+      </c>
+      <c r="D14" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D14" t="s">
-        <v>40</v>
-      </c>
-      <c r="E14" t="s">
-        <v>111</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>114</v>
-      </c>
       <c r="J14" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -2017,22 +2017,22 @@
         <v>2</v>
       </c>
       <c r="B15" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="C15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
         <v>116</v>
       </c>
-      <c r="D15" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" t="s">
+      <c r="F15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="F15" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
@@ -2040,22 +2040,22 @@
         <v>4</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="D16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
@@ -2066,16 +2066,16 @@
         <v>17</v>
       </c>
       <c r="C17" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D17" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E17" t="s">
         <v>17</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>19</v>
@@ -2086,22 +2086,22 @@
         <v>2</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C18" t="s">
+        <v>121</v>
+      </c>
+      <c r="D18" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D18" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" t="s">
-        <v>124</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="J18" s="8" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -2109,22 +2109,22 @@
         <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E19" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J19" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -2135,19 +2135,19 @@
         <v>10</v>
       </c>
       <c r="C20" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D20" t="s">
         <v>16</v>
       </c>
       <c r="E20" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="J20" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
@@ -2155,22 +2155,22 @@
         <v>5</v>
       </c>
       <c r="B21" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C21" t="s">
         <v>12</v>
       </c>
       <c r="D21" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
@@ -2178,22 +2178,22 @@
         <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C22" t="s">
         <v>12</v>
       </c>
       <c r="D22" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
         <v>11</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="J22" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
@@ -2201,22 +2201,22 @@
         <v>2</v>
       </c>
       <c r="B23" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C23" t="s">
         <v>12</v>
       </c>
       <c r="D23" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="J23" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
@@ -2224,19 +2224,19 @@
         <v>1</v>
       </c>
       <c r="B24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" t="s">
+        <v>58</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>59</v>
-      </c>
-      <c r="D24" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="E24" t="s">
-        <v>60</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
@@ -2244,13 +2244,13 @@
         <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C25" t="s">
         <v>20</v>
       </c>
       <c r="D25" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E25" t="s">
         <v>15</v>
@@ -2259,7 +2259,7 @@
         <v>21</v>
       </c>
       <c r="J25" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
@@ -2267,22 +2267,22 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E26" t="s">
         <v>14</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J26" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.25">
@@ -2290,22 +2290,22 @@
         <v>1</v>
       </c>
       <c r="B27" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C27" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D27" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E27" t="s">
         <v>14</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J27" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
@@ -2313,10 +2313,10 @@
         <v>1</v>
       </c>
       <c r="B28" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D28" t="s">
         <v>13</v>
@@ -2325,10 +2325,10 @@
         <v>14</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J28" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.25">
@@ -2342,13 +2342,13 @@
         <v>23</v>
       </c>
       <c r="E30" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>24</v>
+        <v>134</v>
       </c>
       <c r="J30" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -2356,19 +2356,19 @@
         <v>2</v>
       </c>
       <c r="B31" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C31" t="s">
         <v>23</v>
       </c>
       <c r="E31" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>26</v>
+        <v>135</v>
       </c>
       <c r="J31" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
@@ -2379,16 +2379,16 @@
         <v>22</v>
       </c>
       <c r="C32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" t="s">
+        <v>66</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E32" t="s">
-        <v>68</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="J32" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:10" x14ac:dyDescent="0.25">
@@ -2399,16 +2399,16 @@
         <v>22</v>
       </c>
       <c r="C33" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" t="s">
+        <v>71</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E33" t="s">
-        <v>73</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="J33" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="34" spans="1:10" x14ac:dyDescent="0.25">
@@ -2416,7 +2416,7 @@
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B35" s="7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -2424,87 +2424,87 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B37" s="4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B38" s="4" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B39" s="4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="40" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B40" s="4" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B41" s="4" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B42" s="4" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B47" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="F25" r:id="rId1" xr:uid="{00000000-0004-0000-0000-00000F000000}"/>
-    <hyperlink ref="F30" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000013000000}"/>
-    <hyperlink ref="F31" r:id="rId3" xr:uid="{00000000-0004-0000-0000-000014000000}"/>
-    <hyperlink ref="J17" r:id="rId4" xr:uid="{69B674E5-918E-4C55-9473-EE3B4A218C54}"/>
-    <hyperlink ref="F19" r:id="rId5" xr:uid="{A59D37D6-A940-423C-9F03-07E51A21CDF8}"/>
-    <hyperlink ref="F21" r:id="rId6" xr:uid="{82E34BDF-736F-4F98-A76A-B89827876B4D}"/>
-    <hyperlink ref="F22" r:id="rId7" xr:uid="{BA0C518E-2948-45FD-9328-DAE3823EA657}"/>
-    <hyperlink ref="F23" r:id="rId8" xr:uid="{ABDD5C1F-0AC0-49FC-B475-2179875D8E55}"/>
-    <hyperlink ref="F24" r:id="rId9" xr:uid="{4B9DD349-A0F7-425B-94BE-B03C8415B82A}"/>
-    <hyperlink ref="F32" r:id="rId10" xr:uid="{4A11A930-DB4E-4E4A-837D-1777192D19A3}"/>
-    <hyperlink ref="F33" r:id="rId11" xr:uid="{908C5348-17D7-474A-8258-C59855842B28}"/>
-    <hyperlink ref="F26" r:id="rId12" xr:uid="{56A73993-B2DB-4837-AFF8-25F5156F7AF0}"/>
-    <hyperlink ref="F27" r:id="rId13" xr:uid="{D08A31B4-39E6-4E55-8548-0981C02FC257}"/>
-    <hyperlink ref="F28" r:id="rId14" xr:uid="{FE8D99FE-F126-4D68-9F66-9C5F628C4A63}"/>
-    <hyperlink ref="F17" r:id="rId15" xr:uid="{FC450F80-CCB0-4694-BF61-DF1D3F2AF604}"/>
-    <hyperlink ref="F7" r:id="rId16" xr:uid="{60C3DDD5-6905-4E14-B8B5-6A3E9EA0AF6B}"/>
-    <hyperlink ref="F4" r:id="rId17" xr:uid="{59685DFF-3317-4BA8-8E3C-6435C2F76294}"/>
-    <hyperlink ref="F3" r:id="rId18" xr:uid="{6595DF75-EB76-4399-9AED-6F5DE708EA13}"/>
-    <hyperlink ref="F5" r:id="rId19" xr:uid="{B8E6F0B0-6CAB-4C9B-B178-025C349AFA98}"/>
-    <hyperlink ref="F6" r:id="rId20" xr:uid="{CC3D330B-00AE-40E6-92F1-4D1D57138FF9}"/>
-    <hyperlink ref="F8" r:id="rId21" xr:uid="{6BDD6546-E590-407E-BBAC-80DB5C91E1D5}"/>
-    <hyperlink ref="F10" r:id="rId22" xr:uid="{AA5D638E-598C-4688-8A1B-DE6D70B684CC}"/>
-    <hyperlink ref="F9" r:id="rId23" xr:uid="{D643580E-AB4A-44AE-8CA0-AFD7AF320E07}"/>
-    <hyperlink ref="F12" r:id="rId24" xr:uid="{9B95F101-1788-4507-ABDF-76C8857BC01D}"/>
-    <hyperlink ref="F11" r:id="rId25" xr:uid="{5EF6D2E7-E7B9-41A1-B6A0-64ED2D05BEA4}"/>
-    <hyperlink ref="F14" r:id="rId26" xr:uid="{791FEB86-1554-46F2-BD34-2BF4BA7A5E00}"/>
-    <hyperlink ref="F13" r:id="rId27" xr:uid="{BA45706A-4B05-4AA9-8E13-A365CB62C697}"/>
-    <hyperlink ref="F15" r:id="rId28" xr:uid="{74B4066C-996A-4EF0-A408-96B6531BD423}"/>
-    <hyperlink ref="F16" r:id="rId29" xr:uid="{175F7055-DDF5-459D-B50E-65B8F5F5B535}"/>
-    <hyperlink ref="F18" r:id="rId30" xr:uid="{6047317A-8C37-45D1-8033-569CD7EE39BF}"/>
-    <hyperlink ref="F20" r:id="rId31" xr:uid="{569E554E-8A0A-433E-96B7-FF01DF6D4DD0}"/>
+    <hyperlink ref="J17" r:id="rId2" xr:uid="{69B674E5-918E-4C55-9473-EE3B4A218C54}"/>
+    <hyperlink ref="F19" r:id="rId3" xr:uid="{A59D37D6-A940-423C-9F03-07E51A21CDF8}"/>
+    <hyperlink ref="F21" r:id="rId4" xr:uid="{82E34BDF-736F-4F98-A76A-B89827876B4D}"/>
+    <hyperlink ref="F22" r:id="rId5" xr:uid="{BA0C518E-2948-45FD-9328-DAE3823EA657}"/>
+    <hyperlink ref="F23" r:id="rId6" xr:uid="{ABDD5C1F-0AC0-49FC-B475-2179875D8E55}"/>
+    <hyperlink ref="F24" r:id="rId7" xr:uid="{4B9DD349-A0F7-425B-94BE-B03C8415B82A}"/>
+    <hyperlink ref="F32" r:id="rId8" xr:uid="{4A11A930-DB4E-4E4A-837D-1777192D19A3}"/>
+    <hyperlink ref="F33" r:id="rId9" xr:uid="{908C5348-17D7-474A-8258-C59855842B28}"/>
+    <hyperlink ref="F26" r:id="rId10" xr:uid="{56A73993-B2DB-4837-AFF8-25F5156F7AF0}"/>
+    <hyperlink ref="F27" r:id="rId11" xr:uid="{D08A31B4-39E6-4E55-8548-0981C02FC257}"/>
+    <hyperlink ref="F28" r:id="rId12" xr:uid="{FE8D99FE-F126-4D68-9F66-9C5F628C4A63}"/>
+    <hyperlink ref="F17" r:id="rId13" xr:uid="{FC450F80-CCB0-4694-BF61-DF1D3F2AF604}"/>
+    <hyperlink ref="F7" r:id="rId14" xr:uid="{60C3DDD5-6905-4E14-B8B5-6A3E9EA0AF6B}"/>
+    <hyperlink ref="F4" r:id="rId15" xr:uid="{59685DFF-3317-4BA8-8E3C-6435C2F76294}"/>
+    <hyperlink ref="F3" r:id="rId16" xr:uid="{6595DF75-EB76-4399-9AED-6F5DE708EA13}"/>
+    <hyperlink ref="F5" r:id="rId17" xr:uid="{B8E6F0B0-6CAB-4C9B-B178-025C349AFA98}"/>
+    <hyperlink ref="F6" r:id="rId18" xr:uid="{CC3D330B-00AE-40E6-92F1-4D1D57138FF9}"/>
+    <hyperlink ref="F8" r:id="rId19" xr:uid="{6BDD6546-E590-407E-BBAC-80DB5C91E1D5}"/>
+    <hyperlink ref="F10" r:id="rId20" xr:uid="{AA5D638E-598C-4688-8A1B-DE6D70B684CC}"/>
+    <hyperlink ref="F9" r:id="rId21" xr:uid="{D643580E-AB4A-44AE-8CA0-AFD7AF320E07}"/>
+    <hyperlink ref="F12" r:id="rId22" xr:uid="{9B95F101-1788-4507-ABDF-76C8857BC01D}"/>
+    <hyperlink ref="F11" r:id="rId23" xr:uid="{5EF6D2E7-E7B9-41A1-B6A0-64ED2D05BEA4}"/>
+    <hyperlink ref="F14" r:id="rId24" xr:uid="{791FEB86-1554-46F2-BD34-2BF4BA7A5E00}"/>
+    <hyperlink ref="F13" r:id="rId25" xr:uid="{BA45706A-4B05-4AA9-8E13-A365CB62C697}"/>
+    <hyperlink ref="F15" r:id="rId26" xr:uid="{74B4066C-996A-4EF0-A408-96B6531BD423}"/>
+    <hyperlink ref="F16" r:id="rId27" xr:uid="{175F7055-DDF5-459D-B50E-65B8F5F5B535}"/>
+    <hyperlink ref="F18" r:id="rId28" xr:uid="{6047317A-8C37-45D1-8033-569CD7EE39BF}"/>
+    <hyperlink ref="F20" r:id="rId29" xr:uid="{569E554E-8A0A-433E-96B7-FF01DF6D4DD0}"/>
+    <hyperlink ref="F30" r:id="rId30" xr:uid="{2F9FBE5A-78E4-4125-A41D-F65441CBD586}"/>
+    <hyperlink ref="F31" r:id="rId31" xr:uid="{8F5443CB-4E57-4474-B3F0-BE0B16014E41}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="0" verticalDpi="0" r:id="rId32"/>
